--- a/collateral/SimReal-Top100VC-2026.xlsx
+++ b/collateral/SimReal-Top100VC-2026.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>待确认（logo 看不清，按代表投资推断）</t>
+          <t>已核实（f4.fund、Rothschild 均列第 14）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>（被遮挡，无法辨认）</t>
+          <t>Dragoneer Investment Group</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1108,10 +1108,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>已核实（The VC Corner 列 Dragoneer 第 23）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>dragoneer.com</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1619,7 +1623,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>（V 字 logo，可能是 Vy Capital）</t>
+          <t>（可能是 Vy Capital）</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1632,7 +1636,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待确认（xAI 的第三家；logo 是 V 字，没找到排名原文）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -1699,7 +1703,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>（无法辨认）</t>
+          <t>First Round Capital</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1712,10 +1716,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+          <t>已核实（f4.fund 列第 45；logo 是方括号）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>firstround.com</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1779,7 +1787,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>（可能是 Lux Capital）</t>
+          <t>Lux Capital</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1792,10 +1800,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>已核实（f4.fund 列第 48）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>luxcapital.com</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2103,7 +2115,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2468 Ventures（按 logo 文字）</t>
+          <t>2468 Ventures</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2116,7 +2128,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>较可能（logo 文字清楚，Tracxn 显示投过 Anthropic，没找到排名原文）</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -2239,7 +2251,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>TeleSoft（按 logo 文字）</t>
+          <t>（可能是 IDG Capital）</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -2252,7 +2264,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待确认（早期投资 SHEIN、红底白字 logo；没找到排名原文）</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>（带翅膀的 logo，无法辨认）</t>
+          <t>（无法辨认）</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2328,7 +2340,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待确认（没查到）</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -2615,7 +2627,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>（无法辨认）</t>
+          <t>Houston Ventures</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2628,7 +2640,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>已核实（f4.fund 列第 79）</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -3063,7 +3075,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>（CV 开头，可能是 Curative Ventures）</t>
+          <t>Curative Ventures</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -3076,7 +3088,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>较可能（Instil Bio 最大股东，logo 文字吻合；没找到排名原文）</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -3115,7 +3127,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>（圆形 logo，无法辨认）</t>
+          <t>（可能是 Innovation Endeavors）</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -3128,7 +3140,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待确认（领投过 AlphaSense B 轮；没找到排名原文）</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -3209,7 +3221,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>辨认把握：清楚 = logo 文字可读；较清楚 = logo 可辨但有点糊；待确认 = logo 太小或被遮挡，按代表投资推断或暂时空着。</t>
+          <t>辨认把握：清楚 = logo 文字可读；较清楚 = logo 可辨但有点糊；已核实 = 看不清的 logo 已用公开的排名转载（f4.fund、The VC Corner、Rothschild）对上；较可能 = 证据吻合但没找到排名原文；待确认 = 还没查到，括号里是最可能的候选。</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3235,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SimReal-Top100VC-Apollo导入.csv 只含已辨认的机构（Company Name, Website 两列），可以在 Apollo 里用 CSV 导入批量查公司。</t>
+          <t>SimReal-Top100VC-Apollo导入.csv 收了除'待确认'以外的机构（Company Name, Website 两列），可以在 Apollo 里用 CSV 导入批量查公司；'待确认'的几家可以按括号里的候选名单独搜。</t>
         </is>
       </c>
     </row>

--- a/collateral/SimReal-Top100VC-2026.xlsx
+++ b/collateral/SimReal-Top100VC-2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top 100'!$A$1:$F$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top 100'!$A$1:$P$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,15 +434,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,10 +478,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>投资阶段</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>主力阶段</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>适合我们的种子轮</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>种子项目 / 渠道</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>首笔金额</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>领投</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>阶段信息把握</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>阶段来源</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>辨认把握</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>官网域名</t>
         </is>
@@ -494,12 +554,22 @@
           <t>DoorDash</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>sequoiacap.com</t>
         </is>
@@ -522,12 +592,22 @@
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>a16z.com</t>
         </is>
@@ -550,12 +630,22 @@
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>accel.com</t>
         </is>
@@ -578,12 +668,22 @@
           <t>Kuaishou</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>dst-global.com</t>
         </is>
@@ -606,12 +706,22 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>tigerglobal.com</t>
         </is>
@@ -634,12 +744,22 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>indexventures.com</t>
         </is>
@@ -662,12 +782,22 @@
           <t>Mistral AI</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>lsvp.com</t>
         </is>
@@ -690,12 +820,22 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>thrivecap.com</t>
         </is>
@@ -718,12 +858,22 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>foundersfund.com</t>
         </is>
@@ -746,12 +896,22 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>iconiqcapital.com</t>
         </is>
@@ -774,12 +934,22 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>kleinerperkins.com</t>
         </is>
@@ -802,12 +972,22 @@
           <t>Robinhood</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>nea.com</t>
         </is>
@@ -830,12 +1010,22 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>greylock.com</t>
         </is>
@@ -858,12 +1048,22 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund、Rothschild 均列第 14）</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>benchmark.com</t>
         </is>
@@ -886,12 +1086,22 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>bvp.com</t>
         </is>
@@ -914,12 +1124,22 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>khoslaventures.com</t>
         </is>
@@ -942,12 +1162,22 @@
           <t>Athelas</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>generalcatalyst.com</t>
         </is>
@@ -970,12 +1200,22 @@
           <t>Robinhood</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>ribbitcap.com</t>
         </is>
@@ -998,12 +1238,22 @@
           <t>Figure</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1022,12 +1272,22 @@
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>generalatlantic.com</t>
         </is>
@@ -1050,12 +1310,22 @@
           <t>HashiCorp</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>notablecap.com</t>
         </is>
@@ -1078,12 +1348,22 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>ivp.com</t>
         </is>
@@ -1106,12 +1386,22 @@
           <t>Klarna</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>已核实（The VC Corner 列 Dragoneer 第 23）</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>dragoneer.com</t>
         </is>
@@ -1134,12 +1424,22 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>altimeter.com</t>
         </is>
@@ -1162,12 +1462,22 @@
           <t>HashiCorp</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>mayfield.com</t>
         </is>
@@ -1190,12 +1500,22 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>shv.com</t>
         </is>
@@ -1218,12 +1538,22 @@
           <t>AbCellera</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>orbimed.com</t>
         </is>
@@ -1246,12 +1576,22 @@
           <t>Checkout.com</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>insightpartners.com</t>
         </is>
@@ -1274,12 +1614,22 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>coatue.com</t>
         </is>
@@ -1302,12 +1652,22 @@
           <t>Perch</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>sparkcapital.com</t>
         </is>
@@ -1330,12 +1690,22 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>svangel.com</t>
         </is>
@@ -1358,12 +1728,22 @@
           <t>Braze</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>battery.com</t>
         </is>
@@ -1386,12 +1766,22 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1410,12 +1800,22 @@
           <t>Fireblocks</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>paradigm.xyz</t>
         </is>
@@ -1438,12 +1838,22 @@
           <t>CareBridge（看不清）</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>oakhcft.com</t>
         </is>
@@ -1466,12 +1876,22 @@
           <t>Akero Therapeutics</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>atlasventure.com</t>
         </is>
@@ -1494,12 +1914,22 @@
           <t>Devoted Health</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>venrock.com</t>
         </is>
@@ -1522,12 +1952,22 @@
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>meritechcapital.com</t>
         </is>
@@ -1550,12 +1990,22 @@
           <t>Vast</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>nvp.com</t>
         </is>
@@ -1578,12 +2028,22 @@
           <t>Reflection AI</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>较清楚（红色圆形 logo）</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>crv.com</t>
         </is>
@@ -1606,12 +2066,22 @@
           <t>Crusoe</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>baincapitalventures.com</t>
         </is>
@@ -1634,12 +2104,22 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>待确认（xAI 的第三家；logo 是 V 字，没找到排名原文）</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1658,12 +2138,22 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>menlovc.com</t>
         </is>
@@ -1686,12 +2176,22 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>greenoaks.com</t>
         </is>
@@ -1714,12 +2214,22 @@
           <t>Verkada</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 45；logo 是方括号）</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>firstround.com</t>
         </is>
@@ -1742,12 +2252,22 @@
           <t>Chaos Industries</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>8vc.com</t>
         </is>
@@ -1770,12 +2290,22 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>tcv.com</t>
         </is>
@@ -1798,12 +2328,22 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 48）</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>luxcapital.com</t>
         </is>
@@ -1826,12 +2366,22 @@
           <t>Sana Biotechnology</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>archventure.com</t>
         </is>
@@ -1854,12 +2404,22 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>usv.com</t>
         </is>
@@ -1882,12 +2442,22 @@
           <t>Fivetran</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>matrix.vc</t>
         </is>
@@ -1910,12 +2480,22 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1934,12 +2514,22 @@
           <t>Auth0</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>sapphireventures.com</t>
         </is>
@@ -1962,12 +2552,22 @@
           <t>Anduril</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>valorep.com</t>
         </is>
@@ -1990,12 +2590,22 @@
           <t>Inari Medical</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>usvp.com</t>
         </is>
@@ -2018,12 +2628,22 @@
           <t>Groq</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2042,12 +2662,22 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>future.ventures</t>
         </is>
@@ -2070,12 +2700,22 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>madrona.com</t>
         </is>
@@ -2098,12 +2738,22 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>amplifypartners.com</t>
         </is>
@@ -2126,12 +2776,22 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>较可能（logo 文字清楚，Tracxn 显示投过 Anthropic，没找到排名原文）</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2150,12 +2810,22 @@
           <t>RayzeBio</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>versantventures.com</t>
         </is>
@@ -2178,12 +2848,22 @@
           <t>Sportradar</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>revolution.com</t>
         </is>
@@ -2206,12 +2886,22 @@
           <t>Peloton</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>trueventures.com</t>
         </is>
@@ -2234,12 +2924,22 @@
           <t>Alchemy</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>addition.com</t>
         </is>
@@ -2262,12 +2962,22 @@
           <t>SHEIN</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>待确认（早期投资 SHEIN、红底白字 logo；没找到排名原文）</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -2286,12 +2996,22 @@
           <t>Saronic</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2310,12 +3030,22 @@
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>dcvc.com</t>
         </is>
@@ -2338,12 +3068,22 @@
           <t>W 开头的公司（看不清）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>待确认（没查到）</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -2362,12 +3102,22 @@
           <t>Ro</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>firstmark.com</t>
         </is>
@@ -2390,12 +3140,22 @@
           <t>FalconX</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>flybridge.com</t>
         </is>
@@ -2418,12 +3178,22 @@
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>playground.global</t>
         </is>
@@ -2446,12 +3216,22 @@
           <t>Bobbie</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="P73" s="2" t="inlineStr">
         <is>
           <t>bolt.io</t>
         </is>
@@ -2474,12 +3254,22 @@
           <t>Akero Therapeutics</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>venbio.com</t>
         </is>
@@ -2502,12 +3292,22 @@
           <t>Canva</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>felicis.com</t>
         </is>
@@ -2530,12 +3330,22 @@
           <t>Spark Therapeutics</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -2554,12 +3364,22 @@
           <t>Alchemy</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>panteracapital.com</t>
         </is>
@@ -2582,12 +3402,22 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>initialized.com</t>
         </is>
@@ -2610,12 +3440,22 @@
           <t>Sana Biotechnology</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
         <is>
           <t>fprimecapital.com</t>
         </is>
@@ -2638,12 +3478,22 @@
           <t>Oseberg</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 79）</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -2662,12 +3512,22 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>wing.vc</t>
         </is>
@@ -2690,12 +3550,22 @@
           <t>ServiceTitan</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -2714,12 +3584,22 @@
           <t>（看不清）</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>scalevp.com</t>
         </is>
@@ -2742,12 +3622,22 @@
           <t>W 开头的公司（看不清）</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>canaan.com</t>
         </is>
@@ -2770,12 +3660,22 @@
           <t>Fuse</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>multicoin.capital</t>
         </is>
@@ -2798,12 +3698,22 @@
           <t>Etched</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>primary.vc</t>
         </is>
@@ -2826,12 +3736,22 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -2850,12 +3770,22 @@
           <t>BillionToOne</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -2874,12 +3804,22 @@
           <t>Revolut</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -2898,12 +3838,22 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -2922,12 +3872,22 @@
           <t>Opendoor</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -2946,12 +3906,22 @@
           <t>MyoKardia</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
         <is>
           <t>thirdrockventures.com</t>
         </is>
@@ -2974,12 +3944,22 @@
           <t>Pie Insurance</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
         <is>
           <t>greycroft.com</t>
         </is>
@@ -3002,12 +3982,22 @@
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
         <is>
           <t>craftventures.com</t>
         </is>
@@ -3030,12 +4020,22 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
         <is>
           <t>goodwatercap.com</t>
         </is>
@@ -3058,12 +4058,22 @@
           <t>Move Industries</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
         <is>
           <t>polychain.capital</t>
         </is>
@@ -3086,12 +4096,22 @@
           <t>Instil Bio</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>较可能（Instil Bio 最大股东，logo 文字吻合；没找到排名原文）</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -3110,12 +4130,22 @@
           <t>Bridge</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
         <is>
           <t>haun.co</t>
         </is>
@@ -3138,12 +4168,22 @@
           <t>AlphaSense</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>待确认（领投过 AlphaSense B 轮；没找到排名原文）</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -3162,12 +4202,22 @@
           <t>Poppi</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -3186,15 +4236,25 @@
           <t>Metropolis</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>清楚</t>
-        </is>
-      </c>
+      <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F101"/>
+  <autoFilter ref="A1:P101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3205,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3235,6 +4295,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>投资阶段：每家投哪些轮次、主力阶段、有没有专门的种子项目（如 Sequoia Arc、a16z speedrun、Greylock Edge）、首笔金额和是否领投，附来源；'适合我们的种子轮'按对 3 周大的 AI 公司种子轮的可能性分 A / B / C。A 档和把握低的条目由第二个调研员复核过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>SimReal-Top100VC-Apollo导入.csv 收了除'待确认'以外的机构（Company Name, Website 两列），可以在 Apollo 里用 CSV 导入批量查公司；'待确认'的几家可以按括号里的候选名单独搜。</t>
         </is>
       </c>

--- a/collateral/SimReal-Top100VC-2026.xlsx
+++ b/collateral/SimReal-Top100VC-2026.xlsx
@@ -554,16 +554,58 @@
           <t>DoorDash</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>美国早期（种子/A轮）是交易核心，另有成长基金和常青基金持有后期与上市公司</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Sequoia Arc（pre-seed/seed 公司建设项目，每期约10–15家）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Arc 首笔约 $500K–$1M、约10%股权（第三方报道，官方称条款逐案而定）</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>AI、AI基础设施、企业软件、金融科技、消费、医疗；加密少量</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>种子轮可直接找美国合伙人；截至2026年9月底官网未显示新一期 Arc 开放申请，需关注官网（已复核）</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://hub.causo.ai/guides/how-to-apply-to-sequoia-arc-2026
+https://superscout.co/program/sequoia-arc
+https://www.sequoiacap.com</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -592,16 +634,57 @@
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>多阶段平台：早期交易数量多，资金大头在成长期和 AI 基础设施</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>a16z speedrun（加速器，每年两期，已投250+家）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>speedrun：前期 $500K 换10%（SAFE），18个月内下一轮再投 $500K，合计最高 $1M</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>AI、AI基础设施、企业软件、金融科技、加密（a16z crypto）、生物/医疗、国防（American Dynamism）、游戏</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>SR007 将于2026-10-11结束，需在官网确认 SR008 的申请时间；种子轮也可直接找 AI/infra 或 fintech 团队（已复核）</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://a16z.com/applications-for-a16z-speedrun-sr007-are-now-open/
+https://a16z.com/a16z-speedrun-application-winter-spring-2026/</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -630,16 +713,58 @@
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>以 Series A 早期领投为核心，另设 Accel Leaders 成长基金投后期</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Accel Atoms（印度/东南亚 pre-seed 项目；2026年 Atoms AI 期与 Google AI Futures Fund 合作）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Atoms 标准额 $250K（无估值上限可转债）；Atoms AI 期最高 $2M；美国种子轮金额未确认</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>AI、企业软件/SaaS、网络安全、金融科技、消费；加密少量</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Atoms 主要面向印度创始人，美国团队应直接找 Accel US 谈种子/A轮（已复核）</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.ventureintelligence.com/private-equity/accel-expands-pre-seed-program-with-2-new-tracks:-accel-atoms-ai,-atoms-x
+https://www.incorpx.io/grants/accel-atoms-ai-cohort-2026-pre-seed-scaling-program-312
+https://www.accel.com</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -668,16 +793,58 @@
           <t>Kuaishou</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late（偶尔以跟投方参与 Seed / Series A）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>后期成长轮，偏好估值 $1B+ 的互联网/AI 公司</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>约 $50–100M（第三方数据，未经官方确认）</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>消费互联网、AI、金融科技、企业软件</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026年有跟投种子/A轮的记录（如 Gradium、Tsuga），但都不是领投，3周大的公司很难进入其视野</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caplight.com/investor/dst-global
+https://www.briter.co/companies/dst-global-partners
+https://www.premieralts.com/investors/dst-global</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -706,16 +873,58 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Seed（极少）/ Series A / Series B / Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>成长期私募股权和二级市场；PIP 15 过半交易在 A/B 轮，PIP 17 缩至约 $2.2B 并放缓投资节奏</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>无（合伙人承诺 $1B 作为 LP 投给其他种子基金，不是直投项目）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>互联网、企业软件、金融科技、AI、消费</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026年已转向少而精的打法，新投项目很少，种子轮不在优先之列</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.crunchbase.com/venture/report-tiger-global-seed-investing-better-tomorrow-ventures/
+https://www.startupresearcher.com/news/tiger-global-seeks-2-2-billion-for-new-fund-warning-of-ai-bubble
+https://hedgefundalpha.com/news/tiger-global-pip-17-investor-letter/</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -744,16 +953,58 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Series A/B 早期风投加成长基金（成长基金合计 $2.2B），覆盖欧洲、英国、以色列和美国</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Index 种子基金（$400M，2026年7–8月宣布，专投首轮机构融资）</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>AI、AI基础设施、网络安全、金融科技、医疗、企业软件、消费</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>刚募完 $400M 专项种子基金，并明确表示加码 AI，是种子轮的优先目标（已复核）</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>https://pulse2.com/index-ventures-raises-3-5-billion-across-new-seed-venture-and-growth-funds/
+https://sifted.eu/articles/index-ventures-2bn-raise-ai
+https://dealroom.co/news/142415-index-ventures-raises-2b-in-fresh-capital-lifting-total-to-3-5b-across-s/</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -782,16 +1033,56 @@
           <t>Mistral AI</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>多阶段：早期 A 轮加成长期，近年大额押注 AI 模型公司（Mistral、Anthropic 等）</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Lightspeed seed（种子直投业务，未确认有独立品牌项目）</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>AI、AI基础设施、企业软件、网络安全、金融科技、消费；加密少量</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>有长期做种子轮的传统，AI/infra 方向投得活跃，可直接找企业或 AI 方向的合伙人（已复核）</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://lsvp.com</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -820,16 +1111,58 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>大额集中押注后期 AI（OpenAI 等）；2024年募资 $5B，其中 $1B 为早期基金</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>无（有早期基金，但没有命名的种子项目）</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>约 $500K–$50M+（第三方数据）</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>AI（基础模型和应用）、金融科技、企业软件、医疗、消费</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>有早期基金，但种子轮挑得很严、出手少，更常见于 A 轮及以后的重仓</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/thrive-capital
+https://finder.techleap.nl/news/note/thrive-capital-raises-5-billion-to-invest-in-ai
+https://www.tryfundable.ai/investor/thrive-capital</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -858,16 +1191,57 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>早期风投基金加 FF Growth 成长基金，集中押注硬核技术</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>AI、国防/硬科技、航天、金融科技（Ramp）、加密、生物科技</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>降为 B：搜索没找到 2025–2026 年 FF 领投种子轮的公开报道；它能投种子但数量少、挑剔，资金重心在 A 轮以后和 FF Growth，可作为次优先目标（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>https://foundersfund.com
+https://www.roundfunded.com/blogs/top-seed-vc-funds-2026</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -896,16 +1270,58 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Seed（个别）/ Series A（个别）/ Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ICONIQ Growth 以 B 轮及以后的成长期为主，2025年投入 AI 超 $3B</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>成长期约 $5M–$200M（各来源不一致）；早期金额更小，具体未确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>企业软件/SaaS、AI、网络安全、金融科技</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>近年开始选择性投 AI 种子轮（如 Grotto AI、Whirl AI），但限于极高确信度的项目，常规从 B 轮进入</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/iconiq-growth
+https://iconiq.com/llms.txt
+https://www.eaglerockcfo.com/blog/venture-capital-firms/iconiq-review</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -934,16 +1350,57 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026年3月募资 $3.5B：KP22 早期基金 $1B（种子+A轮），KP Select IV 成长基金 $2.5B</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>KP22 早期基金直投种子轮；KP Fellows 是学生实习项目，不是投资工具</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称早期基金 $500K–$5M，未证实）</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>AI（两只基金都以 AI 为主线）、企业软件、金融科技、医疗、硬科技</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>新的 $1B 早期基金明确投种子和 A 轮，AI 方向全力投入，适合优先接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>https://valueaddvc.com/blog/kleiner-perkins-raises-35-billion-across-two-new-ai-funds
+https://pipelineroad.com/news/20260325-kleiner-perkins-raises-1b-early-stage-and-2-5b-growth-funds-</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -972,16 +1429,56 @@
           <t>Robinhood</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>多阶段：科技类早期 A/B 轮加成长期，医疗/生物科技占比也很大</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>无（直投种子轮，未确认有独立品牌项目）</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、金融科技（Robinhood）、医疗/生物科技、消费</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>会做种子轮，但近年 AI 种子轮的领投案例未经搜索核实，建议找科技早期合伙人</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nea.com</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1010,16 +1507,58 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Greylock 17（$1B）专投 Pre-seed、Seed、Series A 的企业和消费软件</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Greylock Edge（面向 pre-idea / pre-seed / seed 创始人的公司建设项目）</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>未确认（Edge 融资方式灵活，可用 SAFE 或定价轮）</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、AI基础设施、网络安全、消费</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>专注最早期的企业 AI/infra，Edge 很适合刚成立的团队（已复核）</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>https://greylock.com/blog/announcing-greylock-17/
+https://techcrunch.com/2023/10/03/greylock-1b-venture-capital-founders-program/amp/
+https://hub.causo.ai/guides/how-to-apply-to-greylock-edge-2026</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1048,16 +1587,56 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（少量）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>小而精的合伙人团队，以领投 Series A 为核心</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>AI（Sierra、LangChain）、企业软件、消费、市场平台</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>主做 A 轮，偶尔领投优质种子轮（如 LangChain），需要合伙人本人高度认可</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.benchmark.com</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund、Rothschild 均列第 14）</t>
@@ -1086,16 +1665,57 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>约70%的投资在种子和 A 轮；2026年9月新募 $5.75B（$1.75B 投种子/早期，$4B 投成长期）</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>无（早期基金直投种子轮，未确认有独立品牌项目）</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>AI 原生公司（2022年以来投了260+家）、AI基础设施、云/企业软件、网络安全、金融科技、医疗</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>新募了 $1.75B 种子/早期资金，AI 投资非常活跃，是种子轮的优先目标（已复核）</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://pulse2.com/bessemer-venture-partners-raises-5-75-billion/
+https://cryptobriefing.com/bessemer-raises-6b-ai-investments/</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1124,16 +1744,57 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>以早期为主；2026年正募至多 $5.5B，大部分投早期 AI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Khosla Ventures 种子系列基金（新一期约 $1B，据 Bloomberg 报道仍在募集，未正式宣布；“Seed F 约 $400M”无法核实，已删除）</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>AI（OpenAI 早期投资人）、AI基础设施、医疗/生物、气候/能源、硬科技</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>种子轮活跃属实；但新基金（种子 $1B + 早期 $2B + 机会基金 $2.5B，合计至多 $5.5B）只是 Bloomberg 报道的在募计划，金额可能变化（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>https://techfundingnews.com/openais-early-backer-khosla-ventures-targets-largest-fund-ever-at-5-5b-with-most-going-to-early-stage-ai-startups/
+https://dealroom.co/news/141179-khosla-ventures-targets-record-5-5b-fund-most-for-early-stage-ai/</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1162,16 +1823,56 @@
           <t>Athelas</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>多阶段平台，资金大头在成长期和医疗转型；早期团队也做种子轮</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>GC seed（早期团队直投，未确认有独立品牌项目）</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AI、医疗健康（重仓）、金融科技、国防/全球韧性、企业软件、气候</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>早期团队覆盖 AI 和金融科技，种子轮可直接接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.generalcatalyst.com</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1200,16 +1901,58 @@
           <t>Robinhood</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>以 A 轮到 B+ 轮的金融科技为主</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方数据从 $500K 到 $100M+ 不等，差异很大）</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>金融科技、加密/数字资产、AI 原生金融产品、消费金融</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>SimReal 的自我改进交易模型与其金融科技/加密主线高度契合，种子轮会选择性参与</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>https://privateequitylist.com/investors/ribbit-capital
+https://superscout.co/investor/ribbit-capital
+https://vcbeast.com/vc-firms/ribbit-capital</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1238,16 +1981,58 @@
           <t>Figure</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth（第三方称以 Seed/A 为主，但查到的领投多为 A 轮及以后）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>成长期深科技大额投资（2025年9月领投 Figure AI $1B C轮，投后估值 $39B）</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>深科技：AI、仿真、量子、复杂工程/机器人</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>更正：第三方资料（f4、Superscout）称它投种子和 A 轮，但能查到的领投是 Figure AI（A 轮、C 轮）和 Hark（2026年5月 A 轮），种子轮实际很少；2019 年成立，规模小（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/parkway
+https://superscout.co/investor/parkway-venture-capital
+https://www.caplight.com/investor/parkway-venture-capital</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1272,16 +2057,56 @@
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全球成长期股权投资</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>科技、金融服务、医疗、消费、气候（BeyondNetZero）</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>纯成长期投资机构，不适合种子轮</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.generalatlantic.com</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1310,16 +2135,58 @@
           <t>HashiCorp</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>以 Series A/B 为主（原 GGV Capital 美国团队，2024年3月拆分独立）</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>约 $5M–$50M（第三方数据，各来源不一致）</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>云/基础设施、企业软件、网络安全、AI、消费、金融科技</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>会做种子轮但以 A/B 轮为主，infra 方向契合度不错</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>https://signal.nfx.com/firms/notable-capital
+https://fundcomb.com/funds/notable-capital
+https://www.cgaa.org/article/notable-capital-ggv</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1348,16 +2215,58 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>成长期，B 轮后段到 IPO 前</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>通常 $20M+（第三方数据）</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI（Perplexity）、消费、金融科技</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>纯成长期投资机构，不适合种子轮，可留到 B 轮以后再接触</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>https://superscout.co/investor/ivp
+https://www.bloombergquint.com/markets/ivp-raises-1-8-billion-fund-for-growth-stage-startups
+https://seedtable.com/investors/ivp</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1386,16 +2295,57 @@
           <t>Klarna</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>后期大额集中持仓（2025年12月募 $4.3B 第七期，每期约15家）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>未确认（通常为数亿美元级别）</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>AI（OpenAI、Anthropic、Helsing）、企业软件、金融科技、消费互联网</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>只投已验证产品市场契合的后期公司，不做种子轮</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>https://finder.techleap.nl/news/feed/dragoneer-raises-4-3b-for-seventh-vc-fund-amid-slow-fundraising-year
+https://aiwiki.ai/wiki/dragoneer</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>已核实（The VC Corner 列 Dragoneer 第 23）</t>
@@ -1424,16 +2374,57 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late / Public（偶尔 Series A）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>公开市场加后期成长轮的跨阶段投资</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方数据从 $1M 到 $25M 不等，相互矛盾）</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>企业软件/云、AI、消费互联网、金融科技</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>以后期和上市公司投资为主；有第三方称其做 pre-seed/seed，但信息互相矛盾，可信度低（已复核）</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>https://privateequitylist.com/investors/altimeter-capital
+https://vcbeast.com/claim/altimeter</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1462,16 +2453,58 @@
           <t>HashiCorp</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>从公司孵化起投（inception），以种子/A 轮为核心</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>AI Start（$250M 种子基金，2023年7月推出，是 Mayfield 第一只种子基金，专投 AI-first 创始人，首笔 $1–4M）；另有 AI Garage（$100M 孵化项目，面向湾区做 AI teammates 的团队，每队最高 $5M）</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>AI Garage 每个团队最高 $5M，另含6个月津贴</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI（AI teammates/agent）、AI基础设施、网络安全、工程生物</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>补充：原表漏了更对口的 AI Start 种子基金（合伙人 Vijay Reddy 专门负责），种子轮应优先走 AI Start（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20230720038405/en
+https://pulse2.com/mayfield-250-million-ai-start-seed-fund-launches/
+https://www.mayfield.com/mayfield-ai-garage-100m-builder-initiative-for-founders-building-ai-teammates/</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1500,16 +2533,58 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>早期（种子/A），以内部孵化并长期持有企业软件/基础设施公司为特色</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>无（以内部孵化为主，无命名种子项目）</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、数据/云基础设施（AI infra 相关）、安全、存储/硬件；不以金融科技、加密、生物科技为主</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>以自孵化项目著称（Snowflake、Pure Storage），外部陌生接触成功率偏低，可试但别抱太高期望</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>https://signal.nfx.com/firms/sutter-hill-ventures
+https://altss.com/profile/sutter-hill-ventures
+https://venturecapitalarchive.com/venture-funds/sutter-hill-ventures-shv-com</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1538,16 +2613,56 @@
           <t>AbCellera</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B / Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>医疗健康私募风投 + 公开市场（含特许权/信贷），偶有早期孵化</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>生物科技、制药、医疗器械、医疗服务；不投 AI/金融科技/加密</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>纯医疗健康投资机构，与 SimReal 方向不符，可跳过</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.orbimed.com</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1576,16 +2691,58 @@
           <t>Checkout.com</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>成长期软件公司（ScaleUp，B 轮及以后）及收购；近年也频繁领投 AI A 轮</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称 $10M 起；2026 年领投的 AI A 轮多在 $13–25M 规模）</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、网络安全、金融科技、数据基础设施</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>以成长期软件为主，偶有种子；近两年 AI A 轮很活跃，3 周公司种子轮不是首选</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>https://neuronfeed.com/investors/insight-partners
+https://superscout.co/investor/insight-partners
+https://aiwiki.ai/wiki/insight_partners/raw</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1614,16 +2771,58 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>成长期/后期私募 + 公开市场对冲基金（全周期交叉投资），早期仅零星</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未确认（仅第三方资料称有早期团队 Coatue Ventures）</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>AI（含 AI infra）、企业软件、消费互联网、金融科技</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>AI 大额后期投资者（OpenAI 等），对 3 周公司的种子轮基本不现实</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>https://vcbeast.com/claim/coatue-ventures
+https://aifunding.me/insights/coatue-ai-portfolio-analysis
+https://theaiinsider.tech/2024/11/05/coatue-raising-1b-to-power-next-generation-of-ai-innovators/</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1652,16 +2851,58 @@
           <t>Perch</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>早期为主（合伙人称约 3/4 交易为早期，A 轮领投为核心），另有成长基金</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>无当前命名项目（2009 年曾推出 Start@Spark，现状未确认）</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称种子/A 约 $1–15M）</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>消费互联网、企业软件、AI（领投过 Anthropic C 轮）、金融科技、媒体</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>以 A 轮领投为主、也做种子，AI 有布局，值得接触</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>https://vcbeast.com/vc-firms/spark-capital
+https://vator.tv/news/show/2009-03-25-spark-capital-starts-seed-stage-investing
+https://techcrunch.com/2013/02/25/boston-based-vc-firm-and-early-twitter-investor-spark-capital-raises-450m-for-fourth-fund</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1690,16 +2931,58 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>种子轮小额跟投（Seed Fund），另有 Growth Fund 投 B 轮及以后</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>无独立对外种子基金（2018年起不再向外部 LP 募种子基金，种子投资继续做）；另有 SV Angel Growth I（$269.4M）和 Growth II（$330M，2025年1月），投 B 轮及以后</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>约 $200K（第三方据其 FAQ）；2018 年曾称 $25K–$100K</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>跟投为主</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>广泛科技：AI、企业软件、消费、金融科技、加密</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>更正种子工具：所谓“Seed Fund”有一家咨询博客说约 $200K/家，但没有找到 2016 年后新募种子基金的记录；仍是小额跟投的种子投资人（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2018/06/01/sv-angel-says-it-wont-be-raising-another-fund-from-outside-investors
+https://www.dakota.com/fundraising-news/san-francisco-vc-sv-angel-raises-330m-for-sophomore-growth-fund
+https://www.eaglerockcfo.com/blog/venture-capital-firms/sv-angel-review</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1728,16 +3011,58 @@
           <t>Braze</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>企业软件与基础设施的成长期/后期及控股收购，早期占比较小</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称种子 $1–5M）</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI/数据基础设施、网络安全、开发者工具、工业科技</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>多阶段软件基金（Battery XV 2026 年 2 月 $3.25B），做早期但以 A 轮及以后为主</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eaglerockcfo.com/blog/venture-capital-firms/battery-ventures-review
+https://neuronfeed.com/investors/battery-ventures
+https://www.siliconreport.com/venture/battery-ventures</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1766,16 +3091,58 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>官网称"invests early"，集中下注，也做后期与二级份额</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称 $5–10M）</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>AI（投过 OpenAI）、金融科技、国防/航天、企业软件、Web3</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Geoff Lewis 创立（洛杉矶/奥斯汀），AI 与金融科技都覆盖，可接触</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>https://bedrockcap.com/geoff-lewis
+https://whisperlist.draftboard.com/vc/e8c8f4c2-1545-4540-8814-94b21488bead/geoff-lewis-bedrock
+https://vcbeast.com/investors/geoff-lewis</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1800,16 +3167,58 @@
           <t>Fireblocks</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>加密/区块链各阶段（含代币）；2026 年 7 月 $1.2B 新基金扩展至 AI 与机器人</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>加密/Web3、DeFi/交易基础设施；2026 年起新增 AI、机器人等前沿科技</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>自进化交易模型与加密交叉点契合度高；AI 是新方向，可重点接触</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theblock.co/post/407617/paradigm-raises-1-2-billion-fourth-fund-crypto-ai-robotics
+https://cryptobriefing.com/paradigm-ai-robotics-expansion/
+https://aiweekly.co/alerts/paradigm-raises-12b-third-fund-expands-from-crypto-into-ai</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1838,16 +3247,58 @@
           <t>CareBridge（看不清）</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>医疗健康与金融科技的 A 轮到成长期</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方说法从 $1–10M 到 $10–50M 不等）</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>医疗健康、金融科技（支付、保险科技、金融基础设施）</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>金融科技是双主线之一，但偏 A/B 轮，种子可试</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>https://venturecapitalarchive.com/venture-funds/oak-hc-ft-oakhcft-com
+https://superscout.co/investor/oak-hc-ft
+https://vcbeast.com/claim/oak-hc-ft</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1876,16 +3327,56 @@
           <t>Akero Therapeutics</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>生物科技种子与 A 轮，多为自身创立/孵化的公司</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>生物科技/药物研发（纯生物医药）</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>纯生物科技，与 AI/金融方向不符</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlasventure.com</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1914,16 +3405,58 @@
           <t>Devoted Health</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Public</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>科技与医疗健康早期（种子/A），另有医疗公开市场/交叉基金</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称 $5–10M）</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、网络安全、国防、医疗健康/生物科技、金融科技</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>科技+医疗双线早期机构，最新 $650M 基金覆盖 AI 与国防，可接触</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>https://mindmaps.femtech.health/firms/3480
+https://hub.waveup.com/funds/venrock
+https://privateequitylist.com/investors/venrock</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1952,16 +3485,56 @@
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>后期成长型软件（C 轮后至 IPO 前后）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、网络安全、消费互联网</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>纯后期成长基金，不投种子，可跳过</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meritechcapital.com</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -1990,16 +3563,58 @@
           <t>Vast</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>早期风投与成长股权并重（2024 年 $3B 基金，总管理 $15.5B）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称起点约 $1M）</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、金融科技/商业服务、消费、医疗健康</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>多阶段大基金，2026 年领投多笔 AI A/B 轮；种子不是主业</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Norwest_Venture_Partners
+https://foundersuite.com/firms/norwest-venture-partners
+https://neuronfeed.com/investors/norwest</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2028,16 +3643,58 @@
           <t>Reflection AI</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>美国种子与 A 轮（CRV XX $750M，2025 年 8 月关闭，只投种子/A，2024 年退还后期基金资金）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>无独立项目（主基金本身即种子/A 基金）</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>企业软件/开发者工具、消费、AI（作为横向能力）、金融科技、网络安全</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>已彻底回归种子/A 领投，阶段正对口，优先接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>https://pulse2.com/crv-750-million-fund-closed-to-lead-seed-and-series-a-rounds
+https://inforcapital.com/funds/crv-20th-flagship-fund/
+https://www.everythingstartups.com/vc-funds/crv</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>较清楚（红色圆形 logo）</t>
@@ -2066,16 +3723,58 @@
           <t>Crusoe</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>孵化+种子到成长全阶段，近年重心为 AI 应用与 AI infra、金融科技</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>BCV Labs（Palo Alto 的 AI 孵化空间）</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>种子约 $1M 起，成长期最高约 $100M（第三方）</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>AI 应用、AI 基础设施、金融科技、商业、网络安全、医疗、物理 AI</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>AI infra + 金融科技双强（投过 Crusoe），BCV Labs 专做 AI 孵化，强烈推荐（已复核）</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>https://cms.baincapitalventures.com/insight/bain-capital-ventures-reimagined
+https://bitscale.ai/directory/bain-capital-ventures-bcv
+https://www.newsbytesapp.com/news/business/bain-capital-ventures-unveils-16b-fund-to-back-ai-startups/tldr</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2104,16 +3803,58 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>迪拜集中型投资机构，重仓少数平台型公司的成长/后期（参与 xAI B、C 轮），也做二级</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>互联网、软件、AI、前沿科技</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>身份待确认；若为 Vy Capital，则是团队极小的成长期集中基金，几乎不投 3 周早期公司（已复核）</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.foundersuite.com/firms/vy-capital
+https://www.tryfundable.ai/investor/vy-capital
+https://app.mergerlinks.com/transactions/2024-05-26-xai</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>待确认（xAI 的第三家；logo 是 V 字，没找到排名原文）</t>
@@ -2138,16 +3879,57 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>早期到成长（A/B 为主），AI 重仓（Anthropic）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Anthology Fund（与 Anthropic 合作，$100M，投 Pre-seed 到 A 轮）</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Anthology：$100K 起 + $25K Anthropic 模型额度</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>AI/AI infra、企业软件、网络安全、金融科技、医疗、消费</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Anthology Fund 可在线申请、尽调较轻，适合 3 周 AI 公司直接申请（已复核）</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/07/17/menlo-ventures-and-anthropic-team-up-on-a-100m-ai-fund
+https://aiwiki.ai/wiki/menlo_ventures</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2176,16 +3958,56 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>少量高集中度的成长期大额押注并长期持有（首支基金曾早期重仓 Coupang）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>消费互联网、企业软件、AI（2023 年起大额投 AI，如 Scale AI、Databricks）</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>成长期集中投资，不做种子，可跳过</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>https://aiwiki.ai/wiki/greenoaks_capital</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2214,16 +4036,58 @@
           <t>Verkada</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>种子轮领投（Fund X 约 $500M，2025 年 9 月）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>本身即种子基金（Fund X）</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称首投约 $0.5–10M，平均约 $3.5M）</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、金融科技、消费、医疗</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>顶级种子领投机构，阶段完全对口，新基金刚募完，优先接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>https://finder.techleap.nl/news/feed/first-round-capital-launches-500m-fund-x
+https://elev-x.com/news-insights/article-first-round-capital-review/
+https://www.roundfunded.com/en/vc/first-round-capital</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 45；logo 是方括号）</t>
@@ -2252,16 +4116,58 @@
           <t>Chaos Industries</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>种子到 A 轮为主，并通过 8VC Build 自建公司</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>8VC Build（孵化/自建公司）</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称 $0.5–15M）</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>国防、物流/供应链、金融科技、医疗健康、AI、企业软件、生命科学</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Joe Lonsdale 创立（奥斯汀），AI 与金融科技都投，种子活跃，值得接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.startuphub.ai/startups/8vc.md
+https://venturecapitalarchive.com/venture-funds/8vc-8vc-com
+https://vcbeast.com/claim/8vc</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2290,16 +4196,56 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late / Public</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>成长期大额投资（软件、金融科技、消费互联网）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>金融科技、企业软件、消费互联网/媒体</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>纯成长期基金，不投种子，可跳过</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tcv.com</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2328,16 +4274,58 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>深科技早期（孵化/种子/A）为主，Lux Ventures IX $1.5B（2026 年 1 月）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>无命名种子基金（第三方提到 Lux Labs 支持学术研究转化）</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称 $100K–$100M）</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>AI（Hugging Face、Runway、Together AI）、国防/航天、制造、生物科技/医疗、金融科技（Ramp）</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>AI 与深科技早期领投，偏好研究型团队，RL 环境方向较契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>https://ecosistemastartup.com/?p=55835
+https://www.aiwiki.ai/wiki/lux_capital
+https://superscout.co/investor/lux-capital</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 48）</t>
@@ -2366,16 +4354,56 @@
           <t>Sana Biotechnology</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>生物科技公司从零创立并大额早期投资</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>生物科技、生命科学、医疗</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>纯生物科技，与 SimReal 方向不符，可跳过</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.archventure.com</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2404,16 +4432,58 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>种子与 A 轮（Core 基金），另有 Opportunity 基金跟进后期、Climate 基金</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>无独立项目（Core 基金即种子/A 基金）</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方多称 $1–6M）</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>加密/Web3（2021 基金预计约 30%）、金融科技、AI、气候、消费网络</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>种子/A 为主，加密与金融科技积累深（Coinbase），交易+AI 方向值得接触（已复核）</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theblock.co/news/deals/2021-01-26-union-square-ventures-crypto-2021-fund-92652
+https://discover.cretech.com/news/usv-closes-on-450m-for-new-funds-adds-two-partners
+https://vcbeast.com/claim/union-square-ventures</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2442,16 +4512,57 @@
           <t>Fivetran</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A（从 idea 阶段到 A 轮）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>AI/前沿技术、企业软件/B2B、金融科技、基础设施、半导体、消费、医疗科技</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>老牌早期基金（1977，现品牌为 Matrix），常领投种子/A 轮，应用 AI 是重点方向，2026 年仍在投种子轮（已复核）</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>https://startupim.com/investor/matrix-partners/raw
+https://www.pitchbook.com/profiles/investor/11237-50</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2480,16 +4591,58 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B / Growth / Late（个别目录列有 Seed，未确认）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late（头部 AI 公司的后期轮）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>AI 价值链、云/数据基础设施、机器人、高速增长软件</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Sol Bier（前 Cruise）2021 年创立，Fund II $2 亿由现代/起亚做锚定 LP，投过 Anthropic/xAI/Perplexity/Mistral；注意不要和布鲁克林的种子基金 Factorial Capital 搞混</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vcaonline.com/news/2025052024/factorial-funds-launches-second-fund-with-200-million/
+https://foundersuite.com/firms/factorial-funds
+https://www.everythingstartups.com/vc-funds/factorial-funds</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2514,16 +4667,57 @@
           <t>Auth0</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>扩张期（B 轮到 IPO 前）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方估算差异大，约 $2M–$50M）</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI/ML 基础设施、数据分析、安全</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>从 SAP 拆分出来的成长期基金，自称已在 60 家 AI 公司投了 $24 亿，但只投已有 PMF 的公司，不适合种子轮</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/sapphire-ventures
+https://www.descubre.vc/sapphire-ventures</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2552,16 +4746,58 @@
           <t>Anduril</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A（Valor Siren Ventures）/ Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late（主基金）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Valor Siren Ventures（早期基金，聚焦食品/零售科技/可持续，不投 AI）</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>主基金：后期科技（航天、国防、AI、电动车）；VSV：食品、零售科技、可持续</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>主基金只做成长/后期；唯一的早期基金 VSV 聚焦食品和零售，和 AI 种子轮不对口</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20220713005232/en/Valor-Siren-Ventures-II-Closes-595M-Fund
+https://pitchbook.com/profiles/fund/16582-42F
+https://www.buyoutsinsider.com/valor-equity-returns-to-market-with-fifth-flagship-targets-1-25-bln-2/</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2590,16 +4826,58 @@
           <t>Inari Medical</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Seed（选择性）/ Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B（以领投为主）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方 $1M–$10M 不等）</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>网络安全、企业/云软件、消费/电商、医疗（器械、生物、医疗 IT）</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>策略是领投 A/B 轮，种子轮只偶尔做；近年医疗器械比重较大，和 AI 交易/数据方向关联较弱</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/u-s-venture-partners-usvp
+https://en.wikipedia.org/wiki/U.S._Venture_Partners
+https://privateequitylist.com/investors/us-venture-partners-usvp</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2628,16 +4906,58 @@
           <t>Groq</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Growth / Late</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>后期/成长期（逐单募资，每年约 6 笔）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>未确认（单笔通常很大，如 Groq 一轮承诺超 $3 亿）</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>后期科技，包括 AI 芯片（Groq）</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Alex Davis 在达拉斯创立，按单个项目募资，只投后期头部公司，不做种子</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/disruptive
+https://review.brunswickgroup.com/article/disruptive-ceo-alex-davis/
+https://news.bloomberglaw.com/private-equity/ai-chip-startup-groq-nears-600-million-fundraising-deal</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -2662,16 +4982,58 @@
           <t>xAI</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Seed / 早期</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>无（主基金本身就投种子和早期）</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>深科技、航天、机器人、能源/气候、食品农业、生命科学、AI</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Jurvetson 和 Saenko 的基金，已连续三期各 $2 亿，主投种子/早期；但偏硬科技，AI 交易/数据方向不是核心</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2023/04/12/talking-with-future-ventures-about-its-new-fund-ai-hype-and-siri-sucking
+https://techcrunch.com/?p=1784340
+https://www.deep-tech-week.com/organizations/future-ventures</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2700,16 +5062,58 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth（Acceleration Fund）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Madrona Venture Labs（孵化工作室，做 Pre-seed/Seed）</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方：历史种子平均约 $4.25M）</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>AI/智能应用、云与 AI 基础设施、企业软件、AI+生物</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>西雅图头部早期基金，主力是种子/A 轮，AI 是核心方向；偏好太平洋西北地区的项目（已复核）</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>https://hub.waveup.com/funds/madrona-venture-group
+https://vcbeast.com/vc-firms/madrona-venture-labs
+https://pulse2.com/madrona-venture-labs-11-million-fifth-fund-ai-companies/amp/</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2738,16 +5142,58 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>第三方：约 $1M–$10M（种子轮常见约 $3M）</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>AI 基础设施、开发者工具、数据/MLOps、安全；Amplify Bio（计算生物）</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2025 年新募约 $9 亿（Fund 6 / 6 Select / Amplify Bio），专投技术型创始人和 AI 基础设施，和 RL 环境方向高度契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.startuphub.ai/investors/amplify-partners
+https://news.crunchbase.com/news/qa-with-amplify-partners-regarding-its-200m-fund-iii
+https://www.evalyze.ai/investors/barr-yaron</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -2776,16 +5222,58 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed（选择性跟进 Series A）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>无（本身即 pre-seed/种子基金）</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>更正：这家机构确实存在，是 Pankaj Kedia 2021 年创立的圣地亚哥单 GP 基金，主投 AI/深科技的 pre-seed 和种子轮（含金融科技），以跟投为主；有资料称它早期投过 Anthropic、OpenAI、CoreWeave，但各来源说法不一（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/2468-ventures
+https://altss.com/profile/2468-ventures
+https://www.caplight.com/investor/2468ventures</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
           <t>较可能（logo 文字清楚，Tracxn 显示投过 Anthropic，没找到排名原文）</t>
@@ -2810,16 +5298,56 @@
           <t>RayzeBio</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（以自建生物公司为主）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>早期生物科技公司孵化与 A/B 轮</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>生物科技/新药研发（只投生物）</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>纯生物医药基金，不投 AI 软件</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.versantventures.com</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2848,16 +5376,58 @@
           <t>Sportradar</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Seed（Rise of the Rest）/ Series A（Revolution Ventures）/ Growth（Revolution Growth）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>未确认（三支基金并行：种子、早期 &lt;$10M、成长期 ≥$10M）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Rise of the Rest Seed Fund（只投硅谷/纽约/波士顿以外的公司）</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Revolution Ventures &lt;$10M；Revolution Growth ≥$10M；Rise of the Rest 第三方称 $100K–$1M</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>消费科技、金融科技、医疗、教育、体育/媒体</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Steve Case 的基金；种子基金只投三大科技中心以外的公司，SimReal 如果在湾区或纽约就不符合</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2019/10/28/revolution-closes-its-second-rise-of-the-rest-fund-with-150-million/
+https://vcbeast.com/vc-firms/revolution-rise-of-the-rest
+https://hub.waveup.com/funds/revolutions-rise-of-the-rest-seed-fund</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2886,16 +5456,58 @@
           <t>Peloton</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>无（主基金本身就投种子）</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>第三方/旧报道：种子 $1M–$3M，Pre-seed 约 $500K–$1M</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>AI 原生应用、企业软件、消费硬件/消费互联网、医疗</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>典型的种子基金，首投后目标持股约 20–25%，近年重点投 AI 原生的早期公司（已复核）</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/true-ventures
+https://techcrunch.com/2016/08/25/true-ventures-just-closed-its-fifth-fund-with-310-million
+https://vcbeast.com/claim/true-ventures</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2924,16 +5536,58 @@
           <t>Alchemy</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Growth（第三方称约 2/3 资金投成长期）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>AI、金融科技、加密（Alchemy、Chainalysis）、网络安全、SaaS、深科技、医疗、能源</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Lee Fixel（前 Tiger）的多阶段基金，种子到成长期都投，但资金主要在后期；AI、金融科技、加密都在覆盖范围</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Lee_Fixel
+https://eu.techcrunch.com/2023/06/14/lee-fixel-addition-fund/
+https://golden.com/wiki/Addition_Ventures-W4ZANRR</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -2962,16 +5616,56 @@
           <t>SHEIN</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Late（主要在中国）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>中国早期至成长期科技与消费公司</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>TMT/科技、消费、医疗、先进制造（以中国市场为主）</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>身份未确认（由 SHEIN 推测）；IDG 资本主要投中国公司，美国 AI 种子轮可能性低；未搜索验证（已复核）</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/IDG_Capital</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>待确认（早期投资 SHEIN、红底白字 logo；没找到排名原文）</t>
@@ -2996,16 +5690,58 @@
           <t>Saronic</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A（也做后续轮跟投）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>无（主基金本身就投种子）</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方数据差异大，约 $300K–$5M）</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI、国防科技（Saronic）</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Raymond Tonsing 的种子基金，2025 年在募第五期，目标 $4 亿（当时已募 $1.6 亿）；合伙人 Varun Gupta 曾在 Affirm 负责数据科学/ML（已复核）</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2025/01/22/raymond-tonsings-caffeinated-capital-seeks-400m-for-fifth-fund/
+https://mercury.com/investor-database/raymond-tonsing
+https://hub.waveup.com/funds/caffeinated-capital</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3030,16 +5766,58 @@
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth（后期主要跟投自己的组合）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>无（DCVC Bio 是单独的生物基金）</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方 $1M–$25M 不等）</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>深科技、应用 AI、计算基础设施、网络安全、地理空间、气候；DCVC Bio 做生物</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>深科技种子/A 轮基金，早期投过 CoreWeave，看重 AI 基础设施和硬核技术（已复核）</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/company/data-collective
+https://www.deep-tech-week.com/organizations/dcvc-fund
+https://www.caplight.com/investor/dcvc-data-collective</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -3068,15 +5846,51 @@
           <t>W 开头的公司（看不清）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>榜单上的机构名无法辨认，需人工核对原图后再查（已复核）</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -3102,16 +5916,58 @@
           <t>Ro</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（第三方另列 Pre-seed）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>第三方：$250K–$10M</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、AI/数据、消费、金融科技、医疗（Ro）</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>纽约头部早期基金，主力是种子/A 轮；合伙人 Matt Turck 长期关注 AI/数据领域（已复核）</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>https://vcbeast.com/claim/firstmark
+https://venturecapitalarchive.com/venture-funds/firstmark-capital-firstmark-com
+https://www.evalyze.ai/investors/rick-heitzmann</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3140,16 +5996,58 @@
           <t>FalconX</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Next Wave（Pre-seed 独立合伙人网络）</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>种子 $1M–$3M（官网 FAQ）</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>AI 优先、金融科技（FalconX）、加密、企业软件、医疗</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>2025 年 9 月发布第七期 $1 亿种子基金，AI 优先，常领投或联合领投，非常对口（已复核）</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flybridge.com/faqs
+https://parse.gl/brands/flybridge-com
+https://www.everythingstartups.com/vc-funds/flybridge</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3178,16 +6076,58 @@
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>首投 $1M–$20M</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>深科技：AI 算力/芯片、机器人、自动化、量子、能源、生物工程</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>偏好硬科技和物理世界技术，喜欢领投并拿董事席位；纯软件 AI 交易/数据方向不太对口</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>https://venturecapitaljournal.com/playground-global-collects-410m-for-third-fund
+https://superscout.co/investor/playground-global
+https://incubatorlist.com/programs/playground-global</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3216,16 +6156,58 @@
           <t>Bobbie</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>无（主基金本身就投 Pre-seed/种子）</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>第三方：首投约 $200K–$1M</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>软硬件结合、消费硬件、IoT、机器人、健康硬件</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>只投硬件早期项目（Fund III 约 $8200 万），和纯软件 AI 不对口；部分资料称已停止新投资，活跃度存疑</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/bolt
+https://kruzeconsulting.com/blog/featured-service-bolt-venture-capital
+https://superscout.co/investor/bolt</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -3254,16 +6236,56 @@
           <t>Akero Therapeutics</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B / Late / Public</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>生物医药 A/B 轮及上市公司</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>生物科技/新药研发（只投生物）</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>纯生物医药基金，不投 AI 软件</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.venbio.com</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3292,16 +6314,58 @@
           <t>Canva</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A（约九成首投在这两个阶段）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>无独立种子基金（主基金 Fund X 直接投种子；Felicis Fellows 是学生人才项目，不是投资项目）</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>AI（约 70% 组合是 AI 原生公司）、基础设施、安全、医疗、金融科技</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>2025 年 6 月募集 $9 亿 Fund X，常领投或联合领投种子/A 轮，AI 是重中之重，非常对口（已复核）</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/videos/2025-06-13/felicis-ventures-raises-its-largest-fund-video
+https://superscout.co/investor/felicis
+https://aifunding.me/insights/felicis-ai-portfolio-analysis</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3330,16 +6394,56 @@
           <t>Spark Therapeutics</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Late / Public（生物医药 crossover）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>后期/crossover 轮及上市公司</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>生物科技/新药研发（只投生物）</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>美国生物医药后期/crossover 基金（注意和巴黎的 Sofinnova Partners 区分），不投 AI</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofinnova.com</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3364,16 +6468,58 @@
           <t>Alchemy</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Public（流动代币）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>加密股权与早期代币（种子到早期为主，另有流动代币策略）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Pantera Early-Stage Token Fund（早期代币基金，非股权种子计划）</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方称约$5M，未经一手来源证实）</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>加密/区块链、Web3基础设施、DeFi；涉及AI×加密</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>顶级加密基金，种子很活跃但只看crypto；SimReal需有链上/加密交易角度才匹配</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>https://panteracapital.com/?p=243
+https://pitchbook.com/profiles/company/60945-31
+https://theblock.co/post/291035/jshubnell@theblock.co</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3402,16 +6548,58 @@
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A（跟进，靠opportunity fund）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>种子轮（产品市场匹配前的软件公司）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>无（本身即种子基金）</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>$1M–$4M（第三方资料）</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>AI、金融科技、企业SaaS、基础设施、市场平台、加密</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Coinbase早期投资人，专做种子且偏好领投；AI+fintech方向高度契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>https://superscout.co/investor/initialized-capital
+https://www.bloombergquint.com/markets/initialized-capital-raises-700-million-launches-2-new-funds
+https://www.caplight.com/investor/initialized-capital-management</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3440,16 +6628,56 @@
           <t>Sana Biotechnology</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>早期（种子到A轮）为主，生命科学与科技两条线</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>生物科技/医疗为主，另有科技线：金融科技、企业软件、前沿科技</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>富达关联基金，生物科技占大头；科技线做金融科技/企业软件早期，可找科技团队</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>https://fprimecapital.com</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3478,16 +6706,58 @@
           <t>Oseberg</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B / Growth（自称早期至成长期；种子未确认）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>能源与工业科技早期至成长期</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>能源科技、工业科技、油气数据软件</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>休斯顿能源/工业科技基金（领投Oseberg A轮），与AI/交易赛道不符</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>https://foundersuite.com/firms/houston-ventures
+https://siliconbayounews.com/tag/oseberg/
+https://www.caplight.com/investor/houven</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>已核实（f4.fund 列第 79）</t>
@@ -3512,16 +6782,58 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A（领投为主），后续轮跟进</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>种子与A轮，企业AI与数据平台</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>$5M–$20M（第三方资料，常见约$10M）</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>企业AI、AI基础设施、数据平台、企业软件</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Snowflake早期投资人，专注AI优先技术栈，领投种子/A轮，非常契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>https://superscout.co/investor/wing-venture-capital
+https://privateequitylist.com/investor/wing-venture-capital
+https://en.wikipedia.org/wiki/Wing_Venture_Capital</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3550,16 +6862,58 @@
           <t>ServiceTitan</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Series B / Growth / Late</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>成长期股权（B轮至Pre-IPO）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>$20M–$150M（第三方资料）</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>垂直SaaS、企业软件</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>成长期垂直SaaS基金，不做种子</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/tidemark
+https://foundersuite.com/firms/tidemark
+https://pitchbook.com/profiles/investor/463466-89</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3584,16 +6938,58 @@
           <t>（看不清）</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B（后续轮跟进）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>A/B轮领投，要求已有首批客户</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>$5M–$50M（官网FAQ）</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>AI、B2B软件、垂直软件、开发者工具、基础设施、安全</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>约80%的A/B轮由其领投，但要有付费客户；种子阶段可先建立关系</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scalevp.com/frequently-asked-questions
+https://www.caplight.com/investor/scale-venture-partners
+https://news.crunchbase.com/venture/scale-venture-partners-raises-400-million-fund-vi-launches-scale-studio-beta/</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3622,16 +7018,57 @@
           <t>W 开头的公司（看不清）</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth（老项目加注）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>种子与早期（Fund XIII $650M 主基金）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>无（主基金直接做种子）</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>种子$1M–$5M；整体$1M–$20M（第三方资料）</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>企业软件、金融科技基础设施、前沿科技（AI/机器人）、消费、医疗/生物科技</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>老牌早期基金，Fund XIII明确投种子，金融科技+AI都在范围内（已复核）</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.citybiz.co/article/401981/canaan-raises-850m-for-fund-xiii/
+https://f4.fund/firms/canaan-partners</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3660,16 +7097,56 @@
           <t>Fuse</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Public（流动代币）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>加密项目早期股权/代币 + 流动代币对冲基金</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>仅加密：DePIN、DeFi、Solana生态</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>纯加密基金，只有在SimReal做链上/加密交易时才有可能</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>https://multicoin.capital</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -3698,16 +7175,58 @@
           <t>Etched</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed（后续轮跟进）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>领投Pre-seed与种子轮（Fund V $625M，2026年2月）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>无（本身即种子基金）</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>平均$5M–$10M（Fund V）</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>金融服务、垂直AI、基础设施与算力、网络安全、医疗、消费、工业</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>纽约种子领投基金，投过Etched，设有金融服务和AI基础设施专属合伙人，高度契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/primary-ventures-raises-healthy-625m-140000268.html
+https://techfundingnews.com/primary-ventures-625m-fund-v-seed-nationwide/
+https://pulse2.com/primary-venture-partners-launches-625-million-fund-v/</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3736,16 +7255,58 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>种子至B轮，常见约$5M</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>$1M–$15M（第三方，常见约$5M）</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>医疗健康、软件、深科技；部分资料含AI、金融科技</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Maverick Capital的创投部门（Coupang为母公司投资），常领投并占董事席位，偏医疗/软件</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>https://venturecapitalarchive.com/venture-funds/maverick-ventures-usa-maverickventures-com
+https://www.everythingstartups.com/vc-funds/maverick-ventures
+https://www.caplight.com/investor/maverick-ventures-1</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3770,16 +7331,58 @@
           <t>BillionToOne</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（Ignite Fund）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed至A轮</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>无（Ignite Fund 投 B 轮及以后）</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>$500K–$10M（第三方资料）</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>AI/机器学习、数据科学、企业软件、医疗（BillionToOne）</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>更正：“2026年6月仍在领投种子”查无实据，能查到的2026年交易只有1月参与 Ventaris Surgical $30M A 轮；管理规模约 $450–480M，正在募第三期基金（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>https://raising.fi/venture-capitalist/neotribe-ventures
+https://www.vcsheet.com/fund/neotribe-ventures
+https://www.caplight.com/investor/neotribe-ventures</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3804,16 +7407,58 @@
           <t>Revolut</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>多阶段，种子/A轮较多，另有成长期机会投资</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>$500K–$10M（第三方资料）</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>AI、金融科技（Revolut）、生物科技、前沿科技</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>纽约多阶段基金（AUM超$5B），做种子且关注AI/金融科技（已复核）</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.abana.co/news/abana-welcomes-new-member-hof-capital/
+https://www.premieralts.com/investors/hof-capital/deals
+https://www.tryfundable.ai/investor/hof-capital</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3838,16 +7483,58 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（以领投 A 轮为主）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>领投A轮为主</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>A轮$5M–$10M（官网FAQ）</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>AI/ML、数据科学、计算机视觉，跨行业（含金融科技）</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>降为 B：官网 FAQ 说主要领投 A 轮（$5–10M），种子轮是次要业务；最新基金是2020年的 Fund III（$288M），之后未见新基金，2026年也没查到领投种子的记录（复核后更正）</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>https://twosigmaventures.com/faq
+https://www.vcaonline.com/news/2020012221/two-sigma-ventures-announces-the-close-of-two-sigma-ventures-iii-lp-a-288m-venture-capital-fund-to-back-data-driven-startups/
+https://seedtable.com/investors/two-sigma-ventures/portfolio</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3872,16 +7559,58 @@
           <t>Opendoor</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>AI公司Pre-seed与种子</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>无（本身即AI种子基金，Fund V $220M，2026年3月）</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>AI、AI基础设施（Lambda、CentML）、AI应用</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>已从Google独立，现名Gradient（Google为LP），AI专属种子基金，首选（已复核）</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>https://globalventuring.com/corporate/information-technology/google-backed-vc-gradient-launches-220m-al-seed-fund/?format=md
+https://www.vcaonline.com/news/2026031722/gradient-raises-220m-fifth-fund-to-seed-next-generation-of-ai-founders/
+https://pulse2.com/gradient-220-million-raised-for-ai-seed-fund/amp/</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3906,16 +7635,56 @@
           <t>MyoKardia</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B（自孵化公司）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>自建生物科技公司并出资A轮</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>仅生物科技/生命科学</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>生物科技公司孵化器，不投AI软件</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdrockventures.com</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3944,16 +7713,56 @@
           <t>Pie Insurance</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>种子至A轮为主，另有成长基金</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>AI、金融科技/保险科技（Pie Insurance）、企业软件、消费</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>纽约/洛杉矶老牌早期基金，种子活跃，覆盖AI与金融科技（已复核）</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greycroft.com</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -3982,16 +7791,58 @@
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>种子与A轮约各占记录投资18%，覆盖至B轮</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方数据冲突，$50K–$50M）</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SaaS、AI（Replit等）、金融科技、市场平台、加密</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>David Sacks联合创立，种子/A轮均做，AI+金融科技契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>https://incubatorlist.com/programs/craft-ventures
+https://vcbeast.com/claim/craft-ventures
+https://aifunding.me/investors/craft-ventures</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -4020,16 +7871,58 @@
           <t>Coupang</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>仅消费科技，约60%资金投早期/种子</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>$1M–$50M（第三方，A/B轮常见约$10M）</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>仅消费科技（含消费金融科技）</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>只投消费科技（Coupang），B2B的AI/数据业务不匹配；交易产品若面向散户可一试</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2023/07/25/exclusive-goodwater-capital-snags-1b-across-two-new-funds-despite-broader-cooling-interest-in-consumer-tech
+https://foundersuite.com/firms/goodwater-capital
+https://superscout.co/investor/goodwater</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -4058,16 +7951,56 @@
           <t>Move Industries</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth / Public（流动代币）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>加密协议早期股权/代币</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>仅加密：L1/L2基础设施（Move Industries）、DeFi、AI×加密</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>顶级加密基金，种子活跃但需加密原生角度</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>https://polychain.capital</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -4096,16 +8029,57 @@
           <t>Instil Bio</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Series A / Series B</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>生物科技早期，常深度参与运营</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>仅生物科技（细胞疗法等）</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>达拉斯生物科技投资方（Instil Bio），与AI赛道无关</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/curative-ventures
+https://pitchbook.com/profiles/fund/16452-10F</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>较可能（Instil Bio 最大股东，logo 文字吻合；没找到排名原文）</t>
@@ -4130,16 +8104,57 @@
           <t>Bridge</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth（早期基金+后期基金）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>加密早期（2026年新募$1B，早期与后期各约$500M）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>B：偶尔投种子 / 以 A 轮为主</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>无（早期基金，无独立品牌计划）</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>加密/区块链为主，扩展至AI Agent、金融科技、另类资产</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Katie Haun创立，新基金明确扩展到AI Agent和“金融新前沿”，可从交易角度切入</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theblock.co/post/399902/crypto-vc-haun-ventures-raises-1-billion-fund-investing-blockchain-ai
+https://www.odaily.news/en/newsflash/479383</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
@@ -4168,16 +8183,57 @@
           <t>AlphaSense</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A（后续轮跟进）</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>种子与A轮（Fund V约$630M，2024年1月，偏Pre-seed/种子）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>A：积极投种子</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>$1M–$15M（第三方资料，有冲突）</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>领投/跟投都做</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>AI/智能软件、计算基础设施、物理经济、医疗、气候</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Eric Schmidt创立，投过AlphaSense，故识别可信；种子AI/基础设施契合（已复核）</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>https://privateequitylist.com/investors/innovation-endeavors
+https://incubatorlist.com/innovation-endeavors</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
           <t>待确认（领投过 AlphaSense B 轮；没找到排名原文）</t>
@@ -4202,16 +8258,58 @@
           <t>Poppi</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Seed / Series A / Series B / Growth</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>消费品牌（食品饮料、美妆、宠物、健康）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>未确认（第三方估计约$1M–$30M）</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>仅消费品/CPG品牌（Poppi）</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>现名CAVU Consumer Partners，专投消费品牌，与AI无关</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>https://f4.fund/firms/cavu-consumer-partners
+https://superscout.co/investor/cavu-consumer-partners
+https://privateequitylist.com/investor/cavu-venture-partners</t>
+        </is>
+      </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
           <t>较清楚</t>
@@ -4236,16 +8334,58 @@
           <t>Metropolis</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Pre-seed / Seed / Series A / Series B / Growth（少量）</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>房地产/建筑科技早期</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>C：不太可能投种子</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>领投为主</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>仅房地产科技、建筑科技、零售科技</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>纽约房地产科技专属基金（$100M），赛道不符</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>https://venturecapitalarchive.com/venture-funds/zigg-capital-ziggcap-com
+https://startupim.com/investor/zigg-capital
+https://www.tryfundable.ai/investor/zigg-capital</t>
+        </is>
+      </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
           <t>清楚</t>
